--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Lithasa.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Lithasa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{102A6B7F-044D-4847-8C31-4EB523215BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{102A6B7F-044D-4847-8C31-4EB523215BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3553DB40-4A1E-4131-803A-4370C674C530}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -327,11 +327,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -351,16 +347,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -771,55 +771,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1"/>
-    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="16" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="17" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.15" customHeight="1">
+    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -833,11 +833,11 @@
       <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="17"/>
+      <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -869,7 +869,7 @@
         <v>0.99999999994179234</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -883,25 +883,25 @@
         <v>44771</v>
       </c>
       <c r="E5" s="5">
-        <v>0.59375</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v>0.75</v>
+        <v>0.99999999994179234</v>
       </c>
       <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>1.7499999999417923</v>
+        <v>1.9999999998835847</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.99999999994179234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="4"/>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="4"/>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="4"/>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
       <c r="D9" s="4"/>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="4"/>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="4"/>
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="4"/>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
       <c r="D13" s="4"/>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="4"/>
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="4"/>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="4"/>
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="4"/>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="4"/>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="4"/>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="4"/>
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="4"/>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
       <c r="D22" s="4"/>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="4"/>
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="4"/>
@@ -1243,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="4"/>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="4"/>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="4"/>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="4"/>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="4"/>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="4"/>
@@ -1351,18 +1351,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>4</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>7</v>
@@ -1399,7 +1399,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="4"/>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="4"/>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="4"/>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="4"/>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="4"/>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="4"/>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="4"/>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="4"/>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="4"/>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="4"/>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="4"/>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="4"/>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="4"/>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="4"/>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="4"/>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="4"/>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:9">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="4"/>
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:9">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="4"/>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:9">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
       <c r="D51" s="4"/>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:9">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
       <c r="D52" s="4"/>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:9">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
       <c r="D53" s="4"/>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:9">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
       <c r="D54" s="4"/>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
       <c r="D55" s="4"/>
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:9">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
       <c r="D56" s="4"/>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:9">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="4"/>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:9">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
       <c r="D58" s="4"/>
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:9">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
       <c r="D59" s="4"/>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:9">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="4"/>
       <c r="G60" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:9">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61" s="4"/>
       <c r="G61" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:9">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62" s="4"/>
       <c r="G62" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:9">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="4"/>
       <c r="G63" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:9">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64" s="4"/>
       <c r="G64" s="6" t="str">
         <f t="shared" si="3"/>
@@ -1960,18 +1960,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>4</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>7</v>
@@ -2008,7 +2008,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G67" s="6" t="str">
         <f t="shared" ref="G67:G98" si="5">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G68" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G69" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G70" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2064,7 +2064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G71" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G72" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G73" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G74" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G75" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G76" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G77" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G78" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G79" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G80" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="7:9">
+    <row r="81" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G81" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="7:9">
+    <row r="82" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G82" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="7:9">
+    <row r="83" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G83" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="7:9">
+    <row r="84" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G84" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="7:9">
+    <row r="85" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G85" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="7:9">
+    <row r="86" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G86" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="7:9">
+    <row r="87" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G87" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="7:9">
+    <row r="88" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G88" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="7:9">
+    <row r="89" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G89" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="7:9">
+    <row r="90" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G90" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="7:9">
+    <row r="91" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G91" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="7:9">
+    <row r="92" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G92" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="7:9">
+    <row r="93" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G93" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="7:9">
+    <row r="94" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G94" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="7:9">
+    <row r="95" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G95" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2414,7 +2414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="7:9">
+    <row r="96" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G96" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G97" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G98" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2456,18 +2456,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>4</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>7</v>
@@ -2504,7 +2504,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G101" s="6" t="str">
         <f t="shared" ref="G101:G132" si="8">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G102" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G103" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G104" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G105" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G106" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G107" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G108" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G109" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G110" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G111" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G112" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="7:9">
+    <row r="113" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G113" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="7:9">
+    <row r="114" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G114" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="7:9">
+    <row r="115" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G115" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="7:9">
+    <row r="116" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G116" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="7:9">
+    <row r="117" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G117" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="7:9">
+    <row r="118" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G118" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="7:9">
+    <row r="119" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G119" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="7:9">
+    <row r="120" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G120" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="7:9">
+    <row r="121" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G121" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="7:9">
+    <row r="122" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G122" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="7:9">
+    <row r="123" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G123" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="7:9">
+    <row r="124" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G124" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="7:9">
+    <row r="125" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G125" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="7:9">
+    <row r="126" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G126" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="7:9">
+    <row r="127" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G127" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="7:9">
+    <row r="128" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G128" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="7:9">
+    <row r="129" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G129" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="7:9">
+    <row r="130" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G130" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="7:9">
+    <row r="131" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G131" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="7:9">
+    <row r="132" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G132" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2954,6 +2954,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2967,18 +2979,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2990,7 +2990,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3002,7 +3002,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
